--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260604.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260604.xlsx
@@ -931,17 +931,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>2,825,000</t>
+          <t>51,268,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>51,268,000</t>
+          <t>2,825,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
